--- a/InputData/hydgn/RPfFHSCC/RPfFHSCC Repayment Period for Financed Hydgn Sector Capital Costs.xlsx
+++ b/InputData/hydgn/RPfFHSCC/RPfFHSCC Repayment Period for Financed Hydgn Sector Capital Costs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\hydgn\RPfFHSCC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\hydgn\RPfFHSCC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43AC5B2D-1799-4DAA-A165-9B7DD15D6CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB53BE95-EDFB-4C86-9DA7-C7BC6B286464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Source:</t>
   </si>
@@ -43,46 +43,34 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>This variable is used with Vensim's DEPRECIATE STRAIGHTLINE function to spread repayment of electricity sector</t>
-  </si>
-  <si>
-    <t>capital costs over a set number of years.</t>
-  </si>
-  <si>
     <t>Unit: years</t>
   </si>
   <si>
     <t>Time Period</t>
   </si>
   <si>
-    <t>boilers</t>
-  </si>
-  <si>
-    <t>nonboiler low temp</t>
-  </si>
-  <si>
-    <t>nonboiler med temp</t>
-  </si>
-  <si>
-    <t>nonboiler high temp</t>
-  </si>
-  <si>
-    <t>cooling</t>
-  </si>
-  <si>
-    <t>machine drive</t>
-  </si>
-  <si>
-    <t>electrochemical</t>
-  </si>
-  <si>
-    <t>other processes</t>
-  </si>
-  <si>
     <t>GET SOURCE</t>
   </si>
   <si>
     <t>RPfFHSCC Repayment Period for Financed Hydrogen Sector Capital Costs</t>
+  </si>
+  <si>
+    <t>hydrogen production</t>
+  </si>
+  <si>
+    <t>This is the number of years over which financed hydrogen production equipment is paid off. EPS uses it to work out the annual loan payment on</t>
+  </si>
+  <si>
+    <t>newly purchased hydrogen production equipment (and the capital recovery factor for hydrogen producers) and to end those payments after this</t>
+  </si>
+  <si>
+    <t>many years. One value applies to every hydrogen production pathway.</t>
+  </si>
+  <si>
+    <t>How the workbook is laid out: this About tab and one data tab, RPfFHSCC, with a single row of data. EPS reads only that row (exported to</t>
+  </si>
+  <si>
+    <t>RPfFHSCC.csv).</t>
   </si>
 </sst>
 </file>
@@ -469,114 +457,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="93" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" s="7"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="2"/>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B23" s="2"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B27" s="2"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
     </row>
@@ -591,82 +582,26 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.54296875" customWidth="1"/>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="3">
         <v>20</v>
       </c>
     </row>
